--- a/output/pdf_financials_xlsx/QIMC.xlsx
+++ b/output/pdf_financials_xlsx/QIMC.xlsx
@@ -431,6 +431,12 @@
   </sheetPr>
   <dimension ref="A1:D135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/QIMC.xlsx
+++ b/output/pdf_financials_xlsx/QIMC.xlsx
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -689,13 +689,13 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>65.495333</v>
+        <v>67.911734</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>81.858633</v>
+        <v>83.202963</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>92.5346</v>
+        <v>119.970602</v>
       </c>
     </row>
     <row r="27">
@@ -1283,7 +1283,7 @@
         <v>0</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>0</v>
+        <v>0.031098</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>0</v>
@@ -3172,7 +3172,11 @@
           <t>Equipment 4</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -4129,7 +4133,11 @@
           <t>Income taxes paid $</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>IncomeTaxPaidSupplementalData</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
@@ -4379,7 +4387,11 @@
           <t>Interest paid $</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>InterestPaidSupplementalData</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -4974,7 +4986,11 @@
           <t>Basic</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
       <c r="E75" s="5" t="n">
         <v>67.911734</v>
       </c>
@@ -5001,7 +5017,11 @@
           <t>Diluted</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>DilutedAverageShares</t>
+        </is>
+      </c>
       <c r="E76" s="5" t="n">
         <v>67.911734</v>
       </c>

--- a/output/pdf_financials_xlsx/QIMC.xlsx
+++ b/output/pdf_financials_xlsx/QIMC.xlsx
@@ -1928,13 +1928,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.720075</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.707277</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.728763</v>
       </c>
     </row>
     <row r="93">
@@ -3044,7 +3044,11 @@
           <t>Share-based payments reserve 10</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -3337,7 +3341,11 @@
           <t>Share-based payments reserve 9</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" s="5" t="n">
         <v>0.720075</v>
       </c>

--- a/output/pdf_financials_xlsx/QIMC.xlsx
+++ b/output/pdf_financials_xlsx/QIMC.xlsx
@@ -2226,10 +2226,10 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.031098</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.15535</v>
       </c>
     </row>
     <row r="112">
@@ -2600,10 +2600,10 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.031098</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.15535</v>
       </c>
     </row>
     <row r="135">
@@ -2616,10 +2616,10 @@
         <v>-1.604345</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-1.197716</v>
+        <v>-1.228814</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-1.44853</v>
+        <v>-1.60388</v>
       </c>
     </row>
   </sheetData>
@@ -3907,7 +3907,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
